--- a/Team-Data/2020-21/1-10-2020-21.xlsx
+++ b/Team-Data/2020-21/1-10-2020-21.xlsx
@@ -806,37 +806,37 @@
         <v>2.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG2" t="n">
         <v>20</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>21</v>
       </c>
       <c r="AH2" t="n">
         <v>15</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AJ2" t="n">
         <v>13</v>
       </c>
       <c r="AK2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AL2" t="n">
         <v>8</v>
       </c>
       <c r="AM2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AN2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
@@ -845,43 +845,43 @@
         <v>4</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AR2" t="n">
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV2" t="n">
         <v>16</v>
       </c>
       <c r="AW2" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX2" t="n">
         <v>28</v>
       </c>
       <c r="AY2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AZ2" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA2" t="n">
         <v>12</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -988,43 +988,43 @@
         <v>1.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>1</v>
       </c>
       <c r="AG3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH3" t="n">
         <v>15</v>
       </c>
       <c r="AI3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AJ3" t="n">
         <v>14</v>
       </c>
       <c r="AK3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AL3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AM3" t="n">
         <v>25</v>
       </c>
       <c r="AN3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO3" t="n">
         <v>22</v>
       </c>
       <c r="AP3" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AQ3" t="n">
         <v>20</v>
@@ -1033,13 +1033,13 @@
         <v>3</v>
       </c>
       <c r="AS3" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV3" t="n">
         <v>23</v>
@@ -1057,10 +1057,10 @@
         <v>22</v>
       </c>
       <c r="BA3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB3" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC3" t="n">
         <v>11</v>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -1092,121 +1092,121 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>5</v>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.455</v>
+        <v>0.5</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>42.3</v>
+        <v>42.2</v>
       </c>
       <c r="J4" t="n">
-        <v>88.5</v>
+        <v>88.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.478</v>
+        <v>0.475</v>
       </c>
       <c r="L4" t="n">
-        <v>14</v>
+        <v>14.4</v>
       </c>
       <c r="M4" t="n">
-        <v>36.5</v>
+        <v>36.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.384</v>
+        <v>0.392</v>
       </c>
       <c r="O4" t="n">
         <v>20</v>
       </c>
       <c r="P4" t="n">
-        <v>24.7</v>
+        <v>24.8</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.806</v>
       </c>
       <c r="R4" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="S4" t="n">
-        <v>38.2</v>
+        <v>38.3</v>
       </c>
       <c r="T4" t="n">
-        <v>46.9</v>
+        <v>47.3</v>
       </c>
       <c r="U4" t="n">
-        <v>25.5</v>
+        <v>25.7</v>
       </c>
       <c r="V4" t="n">
-        <v>16.4</v>
+        <v>16.3</v>
       </c>
       <c r="W4" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="X4" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="Y4" t="n">
         <v>4.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>19.5</v>
+        <v>19.7</v>
       </c>
       <c r="AA4" t="n">
         <v>21.5</v>
       </c>
       <c r="AB4" t="n">
-        <v>118.5</v>
+        <v>118.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD4" t="n">
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AH4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>14</v>
       </c>
-      <c r="AI4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>16</v>
-      </c>
       <c r="AK4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AL4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM4" t="n">
         <v>12</v>
       </c>
       <c r="AN4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AO4" t="n">
         <v>4</v>
       </c>
       <c r="AP4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AQ4" t="n">
         <v>6</v>
@@ -1215,37 +1215,37 @@
         <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AT4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AV4" t="n">
         <v>26</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AX4" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="AY4" t="n">
         <v>6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB4" t="n">
         <v>3</v>
       </c>
       <c r="BC4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -1352,28 +1352,28 @@
         <v>-1.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF5" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG5" t="n">
         <v>15</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>14</v>
       </c>
       <c r="AH5" t="n">
         <v>15</v>
       </c>
       <c r="AI5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ5" t="n">
         <v>19</v>
       </c>
       <c r="AK5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL5" t="n">
         <v>14</v>
@@ -1388,10 +1388,10 @@
         <v>17</v>
       </c>
       <c r="AP5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AR5" t="n">
         <v>9</v>
@@ -1400,13 +1400,13 @@
         <v>21</v>
       </c>
       <c r="AT5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
       </c>
       <c r="AV5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW5" t="n">
         <v>3</v>
@@ -1415,13 +1415,13 @@
         <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ5" t="n">
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>24</v>
@@ -1439,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -1456,142 +1456,142 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>4</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.364</v>
+        <v>0.4</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>41.9</v>
+        <v>41.4</v>
       </c>
       <c r="J6" t="n">
-        <v>87.90000000000001</v>
+        <v>89</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.465</v>
       </c>
       <c r="L6" t="n">
-        <v>13.4</v>
+        <v>12.9</v>
       </c>
       <c r="M6" t="n">
-        <v>35.5</v>
+        <v>35.7</v>
       </c>
       <c r="N6" t="n">
-        <v>0.377</v>
+        <v>0.361</v>
       </c>
       <c r="O6" t="n">
-        <v>18.9</v>
+        <v>19.3</v>
       </c>
       <c r="P6" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8110000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="S6" t="n">
         <v>35</v>
       </c>
       <c r="T6" t="n">
-        <v>43.4</v>
+        <v>43.9</v>
       </c>
       <c r="U6" t="n">
-        <v>24.9</v>
+        <v>24.4</v>
       </c>
       <c r="V6" t="n">
-        <v>17.8</v>
+        <v>17.3</v>
       </c>
       <c r="W6" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X6" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="Y6" t="n">
         <v>4.5</v>
       </c>
       <c r="Z6" t="n">
-        <v>21.5</v>
+        <v>21.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>22.3</v>
+        <v>22.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>116.1</v>
+        <v>115</v>
       </c>
       <c r="AC6" t="n">
-        <v>-5</v>
+        <v>-5.2</v>
       </c>
       <c r="AD6" t="n">
         <v>1</v>
       </c>
       <c r="AE6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG6" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AH6" t="n">
         <v>15</v>
       </c>
       <c r="AI6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AK6" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AM6" t="n">
         <v>14</v>
       </c>
       <c r="AN6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="AO6" t="n">
         <v>8</v>
       </c>
       <c r="AP6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AR6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT6" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AU6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV6" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AW6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>26</v>
@@ -1603,13 +1603,13 @@
         <v>23</v>
       </c>
       <c r="BA6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BB6" t="n">
         <v>6</v>
       </c>
       <c r="BC6" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -1716,49 +1716,49 @@
         <v>-2.1</v>
       </c>
       <c r="AD7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE7" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF7" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG7" t="n">
         <v>15</v>
       </c>
-      <c r="AG7" t="n">
-        <v>14</v>
-      </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ7" t="n">
         <v>21</v>
       </c>
       <c r="AK7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AM7" t="n">
         <v>29</v>
       </c>
       <c r="AN7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO7" t="n">
         <v>30</v>
       </c>
       <c r="AP7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AQ7" t="n">
         <v>30</v>
       </c>
       <c r="AR7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS7" t="n">
         <v>27</v>
@@ -1779,7 +1779,7 @@
         <v>18</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
         <v>8</v>
@@ -1791,7 +1791,7 @@
         <v>30</v>
       </c>
       <c r="BC7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -1898,16 +1898,16 @@
         <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF8" t="n">
         <v>6</v>
       </c>
       <c r="AG8" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH8" t="n">
         <v>5</v>
@@ -1928,34 +1928,34 @@
         <v>7</v>
       </c>
       <c r="AN8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO8" t="n">
         <v>6</v>
       </c>
       <c r="AP8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU8" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AV8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AX8" t="n">
         <v>24</v>
@@ -1967,10 +1967,10 @@
         <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB8" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BC8" t="n">
         <v>7</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2002,130 +2002,130 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F9" t="n">
         <v>5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5</v>
+        <v>0.444</v>
       </c>
       <c r="H9" t="n">
-        <v>49</v>
+        <v>49.1</v>
       </c>
       <c r="I9" t="n">
-        <v>43.2</v>
+        <v>43</v>
       </c>
       <c r="J9" t="n">
-        <v>87.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.494</v>
+        <v>0.489</v>
       </c>
       <c r="L9" t="n">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="M9" t="n">
-        <v>33.5</v>
+        <v>33.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.373</v>
+        <v>0.367</v>
       </c>
       <c r="O9" t="n">
-        <v>17.6</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>23.7</v>
+        <v>25</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.743</v>
+        <v>0.742</v>
       </c>
       <c r="R9" t="n">
-        <v>10.1</v>
+        <v>10.3</v>
       </c>
       <c r="S9" t="n">
-        <v>32.6</v>
+        <v>32.3</v>
       </c>
       <c r="T9" t="n">
         <v>42.7</v>
       </c>
       <c r="U9" t="n">
-        <v>27.1</v>
+        <v>27.6</v>
       </c>
       <c r="V9" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="W9" t="n">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="X9" t="n">
         <v>4.3</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.8</v>
+        <v>20.3</v>
       </c>
       <c r="AA9" t="n">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>116.5</v>
+        <v>116.8</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.7</v>
+        <v>1.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AF9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AG9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AH9" t="n">
         <v>2</v>
       </c>
       <c r="AI9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AJ9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>3</v>
+      </c>
+      <c r="AL9" t="n">
         <v>20</v>
       </c>
-      <c r="AK9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>18</v>
-      </c>
       <c r="AM9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AN9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO9" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT9" t="n">
         <v>25</v>
@@ -2134,28 +2134,28 @@
         <v>2</v>
       </c>
       <c r="AV9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>18</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ9" t="n">
         <v>14</v>
       </c>
-      <c r="AW9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>17</v>
-      </c>
       <c r="BA9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB9" t="n">
         <v>5</v>
       </c>
       <c r="BC9" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2167,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2184,157 +2184,157 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>2</v>
       </c>
       <c r="F10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G10" t="n">
-        <v>0.2</v>
+        <v>0.222</v>
       </c>
       <c r="H10" t="n">
-        <v>49.5</v>
+        <v>49.7</v>
       </c>
       <c r="I10" t="n">
-        <v>38.7</v>
+        <v>39.8</v>
       </c>
       <c r="J10" t="n">
-        <v>92.7</v>
+        <v>93.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.417</v>
+        <v>0.426</v>
       </c>
       <c r="L10" t="n">
-        <v>12.8</v>
+        <v>13.1</v>
       </c>
       <c r="M10" t="n">
-        <v>38.3</v>
+        <v>37.9</v>
       </c>
       <c r="N10" t="n">
-        <v>0.334</v>
+        <v>0.346</v>
       </c>
       <c r="O10" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>23.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.804</v>
       </c>
       <c r="R10" t="n">
         <v>11.1</v>
       </c>
       <c r="S10" t="n">
-        <v>32.6</v>
+        <v>33.2</v>
       </c>
       <c r="T10" t="n">
-        <v>43.7</v>
+        <v>44.3</v>
       </c>
       <c r="U10" t="n">
-        <v>23.6</v>
+        <v>23.9</v>
       </c>
       <c r="V10" t="n">
-        <v>13.4</v>
+        <v>14.1</v>
       </c>
       <c r="W10" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="Y10" t="n">
-        <v>6</v>
+        <v>6.1</v>
       </c>
       <c r="Z10" t="n">
-        <v>19.7</v>
+        <v>19.3</v>
       </c>
       <c r="AA10" t="n">
-        <v>21.4</v>
+        <v>21.9</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.8</v>
+        <v>111.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-6.6</v>
+        <v>-6.2</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF10" t="n">
         <v>28</v>
       </c>
-      <c r="AF10" t="n">
-        <v>29</v>
-      </c>
       <c r="AG10" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AH10" t="n">
         <v>1</v>
       </c>
       <c r="AI10" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
         <v>30</v>
       </c>
       <c r="AL10" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AM10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AO10" t="n">
         <v>11</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>25</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>16</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>9</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>12</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>22</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>27</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>9</v>
+      </c>
+      <c r="BA10" t="n">
         <v>7</v>
       </c>
-      <c r="AS10" t="n">
-        <v>28</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>19</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>5</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>11</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>20</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>26</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>10</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>10</v>
-      </c>
       <c r="BB10" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="BC10" t="n">
         <v>28</v>
@@ -2349,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2366,148 +2366,148 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F11" t="n">
         <v>4</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="H11" t="n">
         <v>48</v>
       </c>
       <c r="I11" t="n">
-        <v>39.9</v>
+        <v>40.1</v>
       </c>
       <c r="J11" t="n">
-        <v>90.3</v>
+        <v>90</v>
       </c>
       <c r="K11" t="n">
-        <v>0.442</v>
+        <v>0.446</v>
       </c>
       <c r="L11" t="n">
-        <v>13.6</v>
+        <v>13.7</v>
       </c>
       <c r="M11" t="n">
-        <v>38.7</v>
+        <v>37.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.351</v>
+        <v>0.361</v>
       </c>
       <c r="O11" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="P11" t="n">
-        <v>25.1</v>
+        <v>25.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.802</v>
       </c>
       <c r="R11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="S11" t="n">
-        <v>35.7</v>
+        <v>35.3</v>
       </c>
       <c r="T11" t="n">
-        <v>44</v>
+        <v>43.2</v>
       </c>
       <c r="U11" t="n">
-        <v>24.9</v>
+        <v>24.3</v>
       </c>
       <c r="V11" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W11" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>6.1</v>
+        <v>5.7</v>
       </c>
       <c r="Y11" t="n">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="Z11" t="n">
-        <v>23.5</v>
+        <v>24.1</v>
       </c>
       <c r="AA11" t="n">
         <v>22.4</v>
       </c>
       <c r="AB11" t="n">
-        <v>113.7</v>
+        <v>114.6</v>
       </c>
       <c r="AC11" t="n">
-        <v>-2.9</v>
+        <v>-3.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF11" t="n">
         <v>6</v>
       </c>
       <c r="AG11" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
         <v>15</v>
       </c>
       <c r="AI11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ11" t="n">
         <v>9</v>
       </c>
       <c r="AK11" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AL11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM11" t="n">
+        <v>10</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>19</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ11" t="n">
         <v>8</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AR11" t="n">
+        <v>24</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AT11" t="n">
         <v>22</v>
       </c>
-      <c r="AO11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>7</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>14</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>19</v>
-      </c>
       <c r="AU11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AV11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW11" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AZ11" t="n">
         <v>29</v>
@@ -2516,10 +2516,10 @@
         <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC11" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2548,115 +2548,115 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>3</v>
       </c>
       <c r="F12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" t="n">
-        <v>0.375</v>
+        <v>0.429</v>
       </c>
       <c r="H12" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I12" t="n">
-        <v>40.3</v>
+        <v>40.7</v>
       </c>
       <c r="J12" t="n">
-        <v>84.90000000000001</v>
+        <v>84.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.474</v>
+        <v>0.484</v>
       </c>
       <c r="L12" t="n">
-        <v>13.3</v>
+        <v>13.4</v>
       </c>
       <c r="M12" t="n">
-        <v>38.6</v>
+        <v>38.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.343</v>
+        <v>0.351</v>
       </c>
       <c r="O12" t="n">
-        <v>19</v>
+        <v>19.4</v>
       </c>
       <c r="P12" t="n">
-        <v>24.9</v>
+        <v>25.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.764</v>
+        <v>0.773</v>
       </c>
       <c r="R12" t="n">
-        <v>7.9</v>
+        <v>7.1</v>
       </c>
       <c r="S12" t="n">
-        <v>34.5</v>
+        <v>35.1</v>
       </c>
       <c r="T12" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U12" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>14.3</v>
       </c>
       <c r="W12" t="n">
         <v>7.3</v>
       </c>
       <c r="X12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.5</v>
+        <v>20.3</v>
       </c>
       <c r="AA12" t="n">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>112.8</v>
+        <v>114.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AE12" t="n">
         <v>25</v>
       </c>
       <c r="AF12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AG12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
         <v>4</v>
       </c>
       <c r="AI12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AJ12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AL12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
         <v>9</v>
       </c>
       <c r="AN12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO12" t="n">
         <v>7</v>
@@ -2665,43 +2665,43 @@
         <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AR12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AS12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AT12" t="n">
         <v>27</v>
       </c>
       <c r="AU12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AX12" t="n">
         <v>1</v>
       </c>
       <c r="AY12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AZ12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BB12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="BC12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2808,10 +2808,10 @@
         <v>5.1</v>
       </c>
       <c r="AD13" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF13" t="n">
         <v>1</v>
@@ -2835,13 +2835,13 @@
         <v>19</v>
       </c>
       <c r="AM13" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AN13" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AP13" t="n">
         <v>23</v>
@@ -2850,7 +2850,7 @@
         <v>20</v>
       </c>
       <c r="AR13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS13" t="n">
         <v>20</v>
@@ -2862,13 +2862,13 @@
         <v>5</v>
       </c>
       <c r="AV13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW13" t="n">
         <v>5</v>
       </c>
       <c r="AX13" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AY13" t="n">
         <v>24</v>
@@ -2877,10 +2877,10 @@
         <v>27</v>
       </c>
       <c r="BA13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BC13" t="n">
         <v>5</v>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -2912,88 +2912,88 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>4</v>
       </c>
       <c r="G14" t="n">
-        <v>0.636</v>
+        <v>0.6</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>40.2</v>
+        <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>85.09999999999999</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.472</v>
+        <v>0.47</v>
       </c>
       <c r="L14" t="n">
-        <v>14.6</v>
+        <v>14.1</v>
       </c>
       <c r="M14" t="n">
-        <v>34.5</v>
+        <v>34.2</v>
       </c>
       <c r="N14" t="n">
-        <v>0.424</v>
+        <v>0.412</v>
       </c>
       <c r="O14" t="n">
-        <v>16.8</v>
+        <v>16.5</v>
       </c>
       <c r="P14" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.841</v>
+        <v>0.846</v>
       </c>
       <c r="R14" t="n">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>41.1</v>
+        <v>41.7</v>
       </c>
       <c r="U14" t="n">
-        <v>24.6</v>
+        <v>24.3</v>
       </c>
       <c r="V14" t="n">
-        <v>14.5</v>
+        <v>14.9</v>
       </c>
       <c r="W14" t="n">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="X14" t="n">
         <v>5</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="Z14" t="n">
-        <v>21.9</v>
+        <v>22.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>111.8</v>
+        <v>110</v>
       </c>
       <c r="AC14" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="AD14" t="n">
         <v>1</v>
       </c>
       <c r="AE14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF14" t="n">
         <v>6</v>
@@ -3005,37 +3005,37 @@
         <v>15</v>
       </c>
       <c r="AI14" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AJ14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AK14" t="n">
         <v>12</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
         <v>18</v>
       </c>
       <c r="AP14" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="AQ14" t="n">
         <v>1</v>
       </c>
       <c r="AR14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS14" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AT14" t="n">
         <v>30</v>
@@ -3044,28 +3044,28 @@
         <v>16</v>
       </c>
       <c r="AV14" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AW14" t="n">
+        <v>23</v>
+      </c>
+      <c r="AX14" t="n">
         <v>17</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>15</v>
       </c>
       <c r="AY14" t="n">
         <v>1</v>
       </c>
       <c r="AZ14" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA14" t="n">
         <v>29</v>
       </c>
       <c r="BB14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="BC14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -3094,82 +3094,82 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.727</v>
+        <v>0.7</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
       </c>
       <c r="I15" t="n">
-        <v>43.3</v>
+        <v>43</v>
       </c>
       <c r="J15" t="n">
-        <v>87.8</v>
+        <v>87.5</v>
       </c>
       <c r="K15" t="n">
-        <v>0.493</v>
+        <v>0.491</v>
       </c>
       <c r="L15" t="n">
-        <v>12</v>
+        <v>12.2</v>
       </c>
       <c r="M15" t="n">
-        <v>31.2</v>
+        <v>31.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.385</v>
+        <v>0.389</v>
       </c>
       <c r="O15" t="n">
-        <v>15.9</v>
+        <v>15.7</v>
       </c>
       <c r="P15" t="n">
-        <v>20.8</v>
+        <v>20.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.764</v>
+        <v>0.766</v>
       </c>
       <c r="R15" t="n">
         <v>9.9</v>
       </c>
       <c r="S15" t="n">
-        <v>38.3</v>
+        <v>38.2</v>
       </c>
       <c r="T15" t="n">
-        <v>48.2</v>
+        <v>48.1</v>
       </c>
       <c r="U15" t="n">
-        <v>25.2</v>
+        <v>24.9</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="W15" t="n">
-        <v>6.5</v>
+        <v>5.8</v>
       </c>
       <c r="X15" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>18.8</v>
+        <v>18.4</v>
       </c>
       <c r="AA15" t="n">
-        <v>20.1</v>
+        <v>19.9</v>
       </c>
       <c r="AB15" t="n">
-        <v>114.5</v>
+        <v>113.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.3</v>
       </c>
       <c r="AD15" t="n">
         <v>1</v>
@@ -3190,13 +3190,13 @@
         <v>4</v>
       </c>
       <c r="AJ15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AM15" t="n">
         <v>24</v>
@@ -3208,16 +3208,16 @@
         <v>20</v>
       </c>
       <c r="AP15" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR15" t="n">
         <v>15</v>
       </c>
       <c r="AS15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AT15" t="n">
         <v>4</v>
@@ -3226,16 +3226,16 @@
         <v>12</v>
       </c>
       <c r="AV15" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AY15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AZ15" t="n">
         <v>7</v>
@@ -3244,10 +3244,10 @@
         <v>16</v>
       </c>
       <c r="BB15" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3259,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -3354,13 +3354,13 @@
         <v>-4</v>
       </c>
       <c r="AD16" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>25</v>
       </c>
       <c r="AF16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG16" t="n">
         <v>26</v>
@@ -3369,10 +3369,10 @@
         <v>5</v>
       </c>
       <c r="AI16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AJ16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AK16" t="n">
         <v>27</v>
@@ -3384,7 +3384,7 @@
         <v>21</v>
       </c>
       <c r="AN16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO16" t="n">
         <v>29</v>
@@ -3393,7 +3393,7 @@
         <v>30</v>
       </c>
       <c r="AQ16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AR16" t="n">
         <v>11</v>
@@ -3402,13 +3402,13 @@
         <v>13</v>
       </c>
       <c r="AT16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU16" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AV16" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AW16" t="n">
         <v>2</v>
@@ -3420,7 +3420,7 @@
         <v>26</v>
       </c>
       <c r="AZ16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BA16" t="n">
         <v>30</v>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -3536,61 +3536,61 @@
         <v>-1.1</v>
       </c>
       <c r="AD17" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE17" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF17" t="n">
         <v>6</v>
       </c>
       <c r="AG17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH17" t="n">
         <v>15</v>
       </c>
       <c r="AI17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
       </c>
       <c r="AK17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AL17" t="n">
         <v>17</v>
       </c>
       <c r="AM17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN17" t="n">
         <v>16</v>
       </c>
       <c r="AO17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AP17" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>14</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>13</v>
       </c>
       <c r="AR17" t="n">
         <v>30</v>
       </c>
       <c r="AS17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU17" t="n">
         <v>4</v>
       </c>
       <c r="AV17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW17" t="n">
         <v>21</v>
@@ -3599,13 +3599,13 @@
         <v>27</v>
       </c>
       <c r="AY17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ17" t="n">
         <v>16</v>
       </c>
       <c r="BA17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BB17" t="n">
         <v>23</v>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -3718,16 +3718,16 @@
         <v>10.6</v>
       </c>
       <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
         <v>5</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>6</v>
       </c>
       <c r="AF18" t="n">
         <v>6</v>
       </c>
       <c r="AG18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH18" t="n">
         <v>15</v>
@@ -3739,7 +3739,7 @@
         <v>8</v>
       </c>
       <c r="AK18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL18" t="n">
         <v>1</v>
@@ -3748,13 +3748,13 @@
         <v>5</v>
       </c>
       <c r="AN18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO18" t="n">
         <v>22</v>
       </c>
       <c r="AP18" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AQ18" t="n">
         <v>18</v>
@@ -3772,7 +3772,7 @@
         <v>7</v>
       </c>
       <c r="AV18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AW18" t="n">
         <v>6</v>
@@ -3781,7 +3781,7 @@
         <v>18</v>
       </c>
       <c r="AY18" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AZ18" t="n">
         <v>10</v>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -3822,157 +3822,157 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>7</v>
       </c>
       <c r="G19" t="n">
-        <v>0.3</v>
+        <v>0.222</v>
       </c>
       <c r="H19" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I19" t="n">
-        <v>40.7</v>
+        <v>41.4</v>
       </c>
       <c r="J19" t="n">
-        <v>91.5</v>
+        <v>92.7</v>
       </c>
       <c r="K19" t="n">
-        <v>0.445</v>
+        <v>0.447</v>
       </c>
       <c r="L19" t="n">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="M19" t="n">
-        <v>34.1</v>
+        <v>35</v>
       </c>
       <c r="N19" t="n">
         <v>0.337</v>
       </c>
       <c r="O19" t="n">
-        <v>15.9</v>
+        <v>15.6</v>
       </c>
       <c r="P19" t="n">
-        <v>21.4</v>
+        <v>21.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.743</v>
+        <v>0.733</v>
       </c>
       <c r="R19" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="S19" t="n">
-        <v>33.2</v>
+        <v>32.1</v>
       </c>
       <c r="T19" t="n">
-        <v>44.9</v>
+        <v>44.1</v>
       </c>
       <c r="U19" t="n">
-        <v>23.5</v>
+        <v>24</v>
       </c>
       <c r="V19" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="W19" t="n">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="X19" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="Y19" t="n">
         <v>5.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>20.9</v>
+        <v>21.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>19.5</v>
+        <v>19.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>108.8</v>
+        <v>110.2</v>
       </c>
       <c r="AC19" t="n">
-        <v>-10</v>
+        <v>-12</v>
       </c>
       <c r="AD19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>27</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>28</v>
+      </c>
+      <c r="AH19" t="n">
         <v>5</v>
       </c>
-      <c r="AE19" t="n">
-        <v>25</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>26</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>27</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>10</v>
-      </c>
       <c r="AI19" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AJ19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK19" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AL19" t="n">
         <v>24</v>
       </c>
       <c r="AM19" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AN19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO19" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AP19" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AQ19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AR19" t="n">
         <v>2</v>
       </c>
       <c r="AS19" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AT19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AW19" t="n">
         <v>13</v>
       </c>
-      <c r="AU19" t="n">
+      <c r="AX19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY19" t="n">
         <v>20</v>
       </c>
-      <c r="AV19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>14</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY19" t="n">
+      <c r="AZ19" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA19" t="n">
         <v>17</v>
       </c>
-      <c r="AZ19" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>22</v>
-      </c>
       <c r="BB19" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC19" t="n">
         <v>30</v>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4082,25 +4082,25 @@
         <v>0.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
         <v>20</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>21</v>
       </c>
       <c r="AH20" t="n">
         <v>5</v>
       </c>
       <c r="AI20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AJ20" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK20" t="n">
         <v>15</v>
@@ -4121,10 +4121,10 @@
         <v>2</v>
       </c>
       <c r="AQ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AS20" t="n">
         <v>8</v>
@@ -4133,7 +4133,7 @@
         <v>3</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV20" t="n">
         <v>27</v>
@@ -4145,13 +4145,13 @@
         <v>25</v>
       </c>
       <c r="AY20" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ20" t="n">
         <v>1</v>
       </c>
       <c r="BA20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB20" t="n">
         <v>25</v>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4186,160 +4186,160 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E21" t="n">
         <v>5</v>
       </c>
       <c r="F21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H21" t="n">
         <v>48</v>
       </c>
       <c r="I21" t="n">
-        <v>37.9</v>
+        <v>38.6</v>
       </c>
       <c r="J21" t="n">
-        <v>84.5</v>
+        <v>85.7</v>
       </c>
       <c r="K21" t="n">
-        <v>0.449</v>
+        <v>0.45</v>
       </c>
       <c r="L21" t="n">
-        <v>9.5</v>
+        <v>9.9</v>
       </c>
       <c r="M21" t="n">
-        <v>26.3</v>
+        <v>26.9</v>
       </c>
       <c r="N21" t="n">
-        <v>0.361</v>
+        <v>0.368</v>
       </c>
       <c r="O21" t="n">
-        <v>16</v>
+        <v>15.7</v>
       </c>
       <c r="P21" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.741</v>
+        <v>0.738</v>
       </c>
       <c r="R21" t="n">
-        <v>10</v>
+        <v>10.2</v>
       </c>
       <c r="S21" t="n">
-        <v>36.1</v>
+        <v>37</v>
       </c>
       <c r="T21" t="n">
-        <v>46.1</v>
+        <v>47.2</v>
       </c>
       <c r="U21" t="n">
-        <v>22.4</v>
+        <v>22.8</v>
       </c>
       <c r="V21" t="n">
         <v>15.7</v>
       </c>
       <c r="W21" t="n">
-        <v>6.9</v>
+        <v>7.2</v>
       </c>
       <c r="X21" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
       <c r="Y21" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="Z21" t="n">
-        <v>20.3</v>
+        <v>20.9</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="AB21" t="n">
-        <v>101.3</v>
+        <v>102.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>-3.8</v>
+        <v>-1.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF21" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="AG21" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AH21" t="n">
         <v>15</v>
       </c>
       <c r="AI21" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AJ21" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AK21" t="n">
         <v>19</v>
       </c>
       <c r="AL21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AM21" t="n">
         <v>30</v>
       </c>
       <c r="AN21" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AO21" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP21" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ21" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR21" t="n">
         <v>14</v>
       </c>
       <c r="AS21" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AT21" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AU21" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AV21" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AX21" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY21" t="n">
+        <v>29</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA21" t="n">
         <v>17</v>
       </c>
-      <c r="AY21" t="n">
+      <c r="BB21" t="n">
         <v>28</v>
       </c>
-      <c r="AZ21" t="n">
-        <v>13</v>
-      </c>
-      <c r="BA21" t="n">
-        <v>15</v>
-      </c>
-      <c r="BB21" t="n">
-        <v>29</v>
-      </c>
       <c r="BC21" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="BD21" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4368,160 +4368,160 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F22" t="n">
         <v>4</v>
       </c>
       <c r="G22" t="n">
-        <v>0.556</v>
+        <v>0.5</v>
       </c>
       <c r="H22" t="n">
         <v>48</v>
       </c>
       <c r="I22" t="n">
-        <v>38.6</v>
+        <v>37.3</v>
       </c>
       <c r="J22" t="n">
-        <v>85.59999999999999</v>
+        <v>85</v>
       </c>
       <c r="K22" t="n">
-        <v>0.451</v>
+        <v>0.438</v>
       </c>
       <c r="L22" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="M22" t="n">
-        <v>40.4</v>
+        <v>40.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.335</v>
+        <v>0.329</v>
       </c>
       <c r="O22" t="n">
-        <v>14.2</v>
+        <v>14</v>
       </c>
       <c r="P22" t="n">
-        <v>19.9</v>
+        <v>20.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.715</v>
+        <v>0.6909999999999999</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="S22" t="n">
-        <v>37.7</v>
+        <v>38.5</v>
       </c>
       <c r="T22" t="n">
-        <v>44.7</v>
+        <v>46</v>
       </c>
       <c r="U22" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V22" t="n">
-        <v>15.4</v>
+        <v>16</v>
       </c>
       <c r="W22" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="X22" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="Y22" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>18.4</v>
+        <v>18</v>
       </c>
       <c r="AA22" t="n">
-        <v>19.2</v>
+        <v>19.4</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.9</v>
+        <v>101.9</v>
       </c>
       <c r="AC22" t="n">
-        <v>-4</v>
+        <v>-6.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE22" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="AF22" t="n">
         <v>6</v>
       </c>
       <c r="AG22" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AH22" t="n">
         <v>15</v>
       </c>
       <c r="AI22" t="n">
+        <v>30</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>26</v>
+      </c>
+      <c r="AK22" t="n">
         <v>28</v>
       </c>
-      <c r="AJ22" t="n">
-        <v>24</v>
-      </c>
-      <c r="AK22" t="n">
-        <v>18</v>
-      </c>
       <c r="AL22" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AM22" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN22" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AO22" t="n">
         <v>27</v>
       </c>
       <c r="AP22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>28</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>11</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>29</v>
+      </c>
+      <c r="AV22" t="n">
+        <v>24</v>
+      </c>
+      <c r="AW22" t="n">
         <v>26</v>
       </c>
-      <c r="AQ22" t="n">
-        <v>27</v>
-      </c>
-      <c r="AR22" t="n">
-        <v>29</v>
-      </c>
-      <c r="AS22" t="n">
-        <v>6</v>
-      </c>
-      <c r="AT22" t="n">
-        <v>14</v>
-      </c>
-      <c r="AU22" t="n">
-        <v>28</v>
-      </c>
-      <c r="AV22" t="n">
-        <v>20</v>
-      </c>
-      <c r="AW22" t="n">
-        <v>23</v>
-      </c>
       <c r="AX22" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY22" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AZ22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="BA22" t="n">
         <v>24</v>
       </c>
       <c r="BB22" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC22" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4533,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4628,16 +4628,16 @@
         <v>-2.4</v>
       </c>
       <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
         <v>5</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>6</v>
       </c>
       <c r="AF23" t="n">
         <v>6</v>
       </c>
       <c r="AG23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AH23" t="n">
         <v>15</v>
@@ -4652,7 +4652,7 @@
         <v>29</v>
       </c>
       <c r="AL23" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AM23" t="n">
         <v>28</v>
@@ -4661,22 +4661,22 @@
         <v>29</v>
       </c>
       <c r="AO23" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>3</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS23" t="n">
         <v>14</v>
       </c>
-      <c r="AP23" t="n">
-        <v>18</v>
-      </c>
-      <c r="AQ23" t="n">
-        <v>4</v>
-      </c>
-      <c r="AR23" t="n">
-        <v>5</v>
-      </c>
-      <c r="AS23" t="n">
-        <v>15</v>
-      </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU23" t="n">
         <v>30</v>
@@ -4697,13 +4697,13 @@
         <v>2</v>
       </c>
       <c r="BA23" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB23" t="n">
         <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4810,28 +4810,28 @@
         <v>4.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>1</v>
       </c>
       <c r="AG24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH24" t="n">
         <v>15</v>
       </c>
       <c r="AI24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ24" t="n">
         <v>21</v>
       </c>
       <c r="AK24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AL24" t="n">
         <v>23</v>
@@ -4843,28 +4843,28 @@
         <v>11</v>
       </c>
       <c r="AO24" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP24" t="n">
         <v>14</v>
-      </c>
-      <c r="AP24" t="n">
-        <v>12</v>
       </c>
       <c r="AQ24" t="n">
         <v>17</v>
       </c>
       <c r="AR24" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AS24" t="n">
         <v>4</v>
       </c>
       <c r="AT24" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AU24" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV24" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW24" t="n">
         <v>8</v>
@@ -4873,16 +4873,16 @@
         <v>2</v>
       </c>
       <c r="AY24" t="n">
+        <v>17</v>
+      </c>
+      <c r="AZ24" t="n">
         <v>15</v>
-      </c>
-      <c r="AZ24" t="n">
-        <v>14</v>
       </c>
       <c r="BA24" t="n">
         <v>11</v>
       </c>
       <c r="BB24" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC24" t="n">
         <v>6</v>
@@ -4897,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -4992,28 +4992,28 @@
         <v>6.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
         <v>1</v>
       </c>
       <c r="AG25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH25" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AJ25" t="n">
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AL25" t="n">
         <v>5</v>
@@ -5025,7 +5025,7 @@
         <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AP25" t="n">
         <v>29</v>
@@ -5034,10 +5034,10 @@
         <v>2</v>
       </c>
       <c r="AR25" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT25" t="n">
         <v>26</v>
@@ -5049,25 +5049,25 @@
         <v>4</v>
       </c>
       <c r="AW25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX25" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AY25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BA25" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BB25" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5079,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -5174,58 +5174,58 @@
         <v>2</v>
       </c>
       <c r="AD26" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AF26" t="n">
         <v>6</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
         <v>5</v>
       </c>
       <c r="AI26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK26" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AL26" t="n">
         <v>2</v>
       </c>
       <c r="AM26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AN26" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO26" t="n">
         <v>9</v>
       </c>
       <c r="AP26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ26" t="n">
         <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AT26" t="n">
         <v>14</v>
       </c>
       <c r="AU26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV26" t="n">
         <v>2</v>
@@ -5240,10 +5240,10 @@
         <v>21</v>
       </c>
       <c r="AZ26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA26" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
         <v>4</v>
@@ -5261,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -5356,25 +5356,25 @@
         <v>-8.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE27" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AF27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG27" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH27" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AI27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AJ27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5386,10 +5386,10 @@
         <v>27</v>
       </c>
       <c r="AN27" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP27" t="n">
         <v>1</v>
@@ -5410,13 +5410,13 @@
         <v>17</v>
       </c>
       <c r="AV27" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AX27" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY27" t="n">
         <v>25</v>
@@ -5425,10 +5425,10 @@
         <v>17</v>
       </c>
       <c r="BA27" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BB27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC27" t="n">
         <v>29</v>
@@ -5443,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -5460,46 +5460,46 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E28" t="n">
         <v>5</v>
       </c>
       <c r="F28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G28" t="n">
-        <v>0.5</v>
+        <v>0.556</v>
       </c>
       <c r="H28" t="n">
-        <v>48.5</v>
+        <v>48.6</v>
       </c>
       <c r="I28" t="n">
-        <v>42</v>
+        <v>42.7</v>
       </c>
       <c r="J28" t="n">
         <v>94.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.445</v>
+        <v>0.452</v>
       </c>
       <c r="L28" t="n">
-        <v>12.1</v>
+        <v>12.6</v>
       </c>
       <c r="M28" t="n">
-        <v>30.9</v>
+        <v>31</v>
       </c>
       <c r="N28" t="n">
-        <v>0.392</v>
+        <v>0.405</v>
       </c>
       <c r="O28" t="n">
-        <v>15</v>
+        <v>15.8</v>
       </c>
       <c r="P28" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.773</v>
+        <v>0.789</v>
       </c>
       <c r="R28" t="n">
         <v>9.300000000000001</v>
@@ -5511,109 +5511,109 @@
         <v>45.4</v>
       </c>
       <c r="U28" t="n">
-        <v>25.5</v>
+        <v>26</v>
       </c>
       <c r="V28" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="W28" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="X28" t="n">
         <v>5.1</v>
       </c>
       <c r="Y28" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.8</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
-        <v>19.4</v>
+        <v>19.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>111.1</v>
+        <v>113.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>-2</v>
+        <v>-1.3</v>
       </c>
       <c r="AD28" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>6</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH28" t="n">
         <v>5</v>
       </c>
-      <c r="AE28" t="n">
-        <v>11</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>15</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>14</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>10</v>
-      </c>
       <c r="AI28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AJ28" t="n">
         <v>1</v>
       </c>
       <c r="AK28" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="AL28" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AM28" t="n">
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AO28" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="AP28" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AQ28" t="n">
+        <v>11</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>17</v>
+      </c>
+      <c r="AS28" t="n">
         <v>12</v>
       </c>
-      <c r="AR28" t="n">
-        <v>18</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>11</v>
-      </c>
       <c r="AT28" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AU28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AV28" t="n">
         <v>1</v>
       </c>
       <c r="AW28" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AY28" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ28" t="n">
         <v>4</v>
       </c>
       <c r="BA28" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BB28" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="BC28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -5642,160 +5642,160 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E29" t="n">
         <v>2</v>
       </c>
       <c r="F29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G29" t="n">
-        <v>0.222</v>
+        <v>0.25</v>
       </c>
       <c r="H29" t="n">
         <v>48</v>
       </c>
       <c r="I29" t="n">
-        <v>39.2</v>
+        <v>39.3</v>
       </c>
       <c r="J29" t="n">
-        <v>89.40000000000001</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>0.439</v>
+        <v>0.443</v>
       </c>
       <c r="L29" t="n">
-        <v>15.2</v>
+        <v>15.5</v>
       </c>
       <c r="M29" t="n">
-        <v>42.3</v>
+        <v>42.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.36</v>
+        <v>0.362</v>
       </c>
       <c r="O29" t="n">
-        <v>17.4</v>
+        <v>17.9</v>
       </c>
       <c r="P29" t="n">
         <v>22.6</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.773</v>
+        <v>0.79</v>
       </c>
       <c r="R29" t="n">
-        <v>9.9</v>
+        <v>9.5</v>
       </c>
       <c r="S29" t="n">
-        <v>33.7</v>
+        <v>33.5</v>
       </c>
       <c r="T29" t="n">
-        <v>43.6</v>
+        <v>43</v>
       </c>
       <c r="U29" t="n">
-        <v>23.2</v>
+        <v>23.6</v>
       </c>
       <c r="V29" t="n">
-        <v>14.2</v>
+        <v>14.5</v>
       </c>
       <c r="W29" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="X29" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="Y29" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>23.4</v>
+        <v>23.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="AB29" t="n">
-        <v>111.1</v>
+        <v>111.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.4</v>
+        <v>-1.5</v>
       </c>
       <c r="AD29" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AE29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF29" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH29" t="n">
         <v>15</v>
       </c>
       <c r="AI29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AK29" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AL29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AM29" t="n">
         <v>1</v>
       </c>
       <c r="AN29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO29" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AP29" t="n">
         <v>16</v>
       </c>
       <c r="AQ29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR29" t="n">
         <v>16</v>
       </c>
       <c r="AS29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AT29" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU29" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AV29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AW29" t="n">
         <v>7</v>
       </c>
       <c r="AX29" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="AY29" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AZ29" t="n">
         <v>28</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BB29" t="n">
         <v>16</v>
       </c>
       <c r="BC29" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5807,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -5824,139 +5824,139 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" t="n">
         <v>4</v>
       </c>
       <c r="G30" t="n">
-        <v>0.6</v>
+        <v>0.556</v>
       </c>
       <c r="H30" t="n">
         <v>48</v>
       </c>
       <c r="I30" t="n">
-        <v>40.4</v>
+        <v>41</v>
       </c>
       <c r="J30" t="n">
-        <v>89.2</v>
+        <v>90</v>
       </c>
       <c r="K30" t="n">
-        <v>0.453</v>
+        <v>0.456</v>
       </c>
       <c r="L30" t="n">
-        <v>15.1</v>
+        <v>15.6</v>
       </c>
       <c r="M30" t="n">
-        <v>40.3</v>
+        <v>40.9</v>
       </c>
       <c r="N30" t="n">
-        <v>0.375</v>
+        <v>0.38</v>
       </c>
       <c r="O30" t="n">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="P30" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.697</v>
+        <v>0.699</v>
       </c>
       <c r="R30" t="n">
-        <v>11.6</v>
+        <v>11.1</v>
       </c>
       <c r="S30" t="n">
-        <v>38.8</v>
+        <v>37.9</v>
       </c>
       <c r="T30" t="n">
-        <v>50.4</v>
+        <v>49</v>
       </c>
       <c r="U30" t="n">
-        <v>22.1</v>
+        <v>22.7</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="X30" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y30" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AA30" t="n">
-        <v>19.2</v>
+        <v>18.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>109.5</v>
+        <v>111</v>
       </c>
       <c r="AC30" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
       <c r="AD30" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="AE30" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AF30" t="n">
         <v>6</v>
       </c>
       <c r="AG30" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AH30" t="n">
         <v>15</v>
       </c>
       <c r="AI30" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AJ30" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AK30" t="n">
         <v>17</v>
       </c>
       <c r="AL30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AM30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN30" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AO30" t="n">
         <v>28</v>
       </c>
       <c r="AP30" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AR30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AT30" t="n">
         <v>1</v>
       </c>
       <c r="AU30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AV30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AW30" t="n">
         <v>30</v>
@@ -5965,19 +5965,19 @@
         <v>9</v>
       </c>
       <c r="AY30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AZ30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BB30" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="BC30" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
@@ -6084,16 +6084,16 @@
         <v>-3</v>
       </c>
       <c r="AD31" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AE31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AF31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG31" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AH31" t="n">
         <v>15</v>
@@ -6102,16 +6102,16 @@
         <v>3</v>
       </c>
       <c r="AJ31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK31" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL31" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AM31" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="n">
         <v>8</v>
@@ -6126,22 +6126,22 @@
         <v>19</v>
       </c>
       <c r="AR31" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AS31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AT31" t="n">
         <v>29</v>
       </c>
       <c r="AU31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV31" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AW31" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX31" t="n">
         <v>29</v>
@@ -6153,7 +6153,7 @@
         <v>30</v>
       </c>
       <c r="BA31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BB31" t="n">
         <v>2</v>
@@ -6171,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-10-2020-21</t>
+          <t>2021-01-10</t>
         </is>
       </c>
     </row>
